--- a/data_extactor/batch_10_fa/trimmed/batch_0048_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0048_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم پایه</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | تفکر انتقادی | نگارش | یادگیری فعال | نظارت | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتریان و خدمات فردی | شیمی</t>
+          <t>پزشکی و دندان‌پزشکی | زیست‌شناسی | روان‌شناسی | درمان و مشاوره | خدمات مشتری و شخصی | شیمی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>متخصصان طب سوزنی | متخصصان کایروپراکتیک | پزشکان عمومی و خانواده | پزشکان متخصص داخلی | پرستاران متخصص بالینی | متخصصان طب فیزیکی و توان‌بخشی</t>
+          <t>متخصصان و کارشناسان طب سوزنی | کایروپراکتورها / متخصصان درمان دستی | پزشکان عمومی و خانواده | پزشکان متخصص بیماری‌های داخلی | پرستاران بالینی پیشرفته | متخصصان طب فیزیکی و توانبخشی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | علوم پایه | نگارش | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | علوم | نگارش | راهبردهای یادگیری | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | روان‌شناسی | زیست‌شناسی</t>
+          <t>زبان انگلیسی | پزشکی و دندان‌پزشکی | خدمات مشتری و شخصی | آموزش و پرورش | روان‌شناسی | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>متخصصان مغز و اعصاب | فن‌آوران بینایی و چشم‌پزشکی | چشم‌پزشکان، به جز اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | پزشکان اطفال، عمومی | متخصصان طب فیزیکی و توان‌بخشی | دستیاران پزشک</t>
+          <t>متخصصان مغز و اعصاب | کارشناسان فناوری پزشکی چشم | متخصصان چشم‌پزشکی، غیر از اطفال | بینایی‌سنج‌ها (اپتومتریست‌ها) | متخصصان عمومی کودکان | متخصصان طب فیزیکی و توانبخشی | دستیاران پزشک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | علوم پایه | شنیدن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش | سخن گفتن | ریاضیات</t>
+          <t>تفکر انتقادی | علوم | گوش دادن فعال | درک مطلب | نظارت | یادگیری فعال | نگارش | سخن گفتن | ریاضیات</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>شیمی | خدمات مشتریان و خدمات فردی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات | پزشکی و دندان‌پزشکی</t>
+          <t>شیمی | خدمات مشتری و شخصی | رایانه و الکترونیک | زیست‌شناسی | ریاضیات | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>دید نزدیک | استدلال استقرایی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | درک شفاهی | استدلال قیاسی</t>
+          <t>بینایی نزدیک | استدلال استقرایی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | درک شفاهی | استدلال قیاسی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها | کارشناسان پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | خون‌گیرها (فلبوتومیست‌ها)</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | کارشناسان سیتوژنتیک | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان و تکنسین‌های خون‌گیری</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | علوم پایه | نظارت | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | علوم | نظارت | ریاضیات</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | مرتب‌سازی اطلاعات | دید نزدیک | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | سیتوتکنولوژیست‌ها | متخصصان ژنتیک | کارشناسان پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی</t>
+          <t>تکنسین‌های علوم زیستی | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | متخصصان ژنتیک | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | زیست‌شناسان سلولی و مولکولی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | سخن گفتن | نظارت | یادگیری فعال | نگارش</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | امور اداری</t>
+          <t>زیست‌شناسی | پزشکی و دندان‌پزشکی | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | دید نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بینایی نزدیک | استدلال استقرایی | حساسیت به مسئله | استدلال قیاسی | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان سیتوژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | خون‌گیرها (فلبوتومیست‌ها) | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها)</t>
+          <t>کارشناسان سیتوژنتیک | کاردان‌های پاتولوژی و بافت‌شناسی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های خون‌گیری | پزشکان متخصص پاتولوژی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | شنیدن فعال | یادگیری فعال | نگارش | علوم پایه</t>
+          <t>درک مطلب | نظارت | تفکر انتقادی | سخن گفتن | گوش دادن فعال | یادگیری فعال | نگارش | علوم</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>زیست‌شناسی | تولید و فرآوری | شیمی | خدمات مشتریان و خدمات فردی | زبان انگلیسی | امور اداری | آموزش و تدریس</t>
+          <t>زیست‌شناسی | تولید و فرآوری | شیمی | خدمات مشتری و شخصی | زبان انگلیسی | اداری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>دید نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | مرتب‌سازی اطلاعات | چابکی انگشتان</t>
+          <t>بینایی نزدیک | درک کتبی | ثبات دست و بازو | درک شفاهی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها | کاردان‌های پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها)</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | کاردان‌های پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | پزشکان متخصص پاتولوژی</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | علوم پایه | نظارت | نگارش | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | علوم | نظارت | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | ریاضیات | خدمات مشتریان و خدمات فردی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی</t>
+          <t>شیمی | زیست‌شناسی | ریاضیات | خدمات مشتری و شخصی | ایمنی و امنیت عمومی | پزشکی و دندان‌پزشکی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>دید نزدیک | حساسیت به مسئله | مرتب‌سازی اطلاعات | بیان شفاهی | درک شفاهی | چابکی انگشتان | درک کتبی</t>
+          <t>بینایی نزدیک | حساسیت به مسئله | ترتیب‌دهی اطلاعات | بیان شفاهی | درک شفاهی | مهارت انگشتان | درک کتبی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان علوم آزمایشگاهی بالینی | خون‌گیرها (فلبوتومیست‌ها) | کارشناسان و تکنسین‌های رادیولوژی</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | کاردان‌های پاتولوژی و بافت‌شناسی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و تکنسین‌های خون‌گیری | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نظارت | سخن گفتن | علوم پایه | نگارش</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نظارت | سخن گفتن | علوم | نگارش</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>شیمی | زیست‌شناسی | زبان انگلیسی | امور اداری</t>
+          <t>شیمی | زیست‌شناسی | زبان انگلیسی | اداری</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>دید نزدیک | چابکی انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>بینایی نزدیک | مهارت انگشتان | درک شفاهی | ثبات دست و بازو | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>تکنسین‌های زیست‌شناسی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها | کارشناسان پاتولوژی و بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | آسیب‌شناسان بالینی و تشریحی (پاتولوژیست‌ها)</t>
+          <t>تکنسین‌های علوم زیستی | تکنسین‌های شیمی | سیتوتکنولوژیست‌ها / کارشناسان سیتولوژی | هیستوتکنولوژیست‌ها / کارشناسان بافت‌شناسی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | پزشکان متخصص پاتولوژی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | علوم پایه</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | نظارت | درک مطلب | نگارش | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | پزشکی و دندان‌پزشکی | زبان انگلیسی | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | پزشکی و دندان‌پزشکی | زبان انگلیسی | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | دید نزدیک | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | بینایی نزدیک | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | سونوگرافیست‌های تشخیصی | تکنسین‌های فوریت‌های پزشکی (EMT) | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان پزشکی هسته‌ای | کارشناسان و تکنسین‌های رادیولوژی | متخصصان درمان تنفسی</t>
+          <t>متخصصان بیماری‌های قلب و عروق | سونوگرافیست‌های تشخیصی / کارشناسان سونوگرافی | تکنسین‌های فوریت‌های پزشکی | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | کارشناسان مراقبت‌های تنفسی / تنفس‌درمانگران</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | علوم پایه | نگارش | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | نظارت | تفکر انتقادی | یادگیری فعال | علوم | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | فیزیک | پزشکی و دندان‌پزشکی | امور اداری | رایانه و الکترونیک | آموزش و تدریس</t>
+          <t>خدمات مشتری و شخصی | فیزیک | پزشکی و دندان‌پزشکی | اداری | رایانه و الکترونیک | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | دید نزدیک | دقت کنترل | ثبات دست و بازو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | بینایی نزدیک | دقت کنترل | ثبات دست و بازو</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>متخصصان قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان پزشکی هسته‌ای | پرتو‌درمانگران (تکنولوژیست‌های رادیوتراپی) | کارشناسان و تکنسین‌های رادیولوژی | رادیولوژیست‌ها</t>
+          <t>متخصصان بیماری‌های قلب و عروق | کارشناسان و تکنسین‌های قلب و عروق | کارشناسان تصویربرداری تشدید مغناطیسی (MRI) | کارشناسان و تکنسین‌های پزشکی هسته‌ای | پرتودرمانگران / کارشناسان رادیوتراپی | کارشناسان و تکنسین‌های رادیولوژی و پرتونگاری | متخصصان رادیولوژی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
